--- a/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
+++ b/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
@@ -570,7 +570,7 @@
         <v>ชาย</v>
       </c>
       <c r="I5" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -605,7 +605,7 @@
         <v>หญิง</v>
       </c>
       <c r="I6" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -640,7 +640,7 @@
         <v>หญิง</v>
       </c>
       <c r="I7" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -675,7 +675,7 @@
         <v>หญิง</v>
       </c>
       <c r="I8" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -710,7 +710,7 @@
         <v>ชาย</v>
       </c>
       <c r="I9" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -745,7 +745,7 @@
         <v>ชาย</v>
       </c>
       <c r="I10" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -780,7 +780,7 @@
         <v>ชาย</v>
       </c>
       <c r="I11" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -815,7 +815,7 @@
         <v>ชาย</v>
       </c>
       <c r="I12" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -850,7 +850,7 @@
         <v>หญิง</v>
       </c>
       <c r="I13" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -885,7 +885,7 @@
         <v>หญิง</v>
       </c>
       <c r="I14" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -920,7 +920,7 @@
         <v>หญิง</v>
       </c>
       <c r="I15" t="str">
-        <v>ฟุตบอล, สแตนเชียร์</v>
+        <v>ฟุตบอล, ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J15" t="str">
         <v>085-226-6457</v>
@@ -955,7 +955,7 @@
         <v>ชาย</v>
       </c>
       <c r="I16" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -990,7 +990,7 @@
         <v>ชาย</v>
       </c>
       <c r="I17" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1025,7 +1025,7 @@
         <v>หญิง</v>
       </c>
       <c r="I18" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1060,7 +1060,7 @@
         <v>หญิง</v>
       </c>
       <c r="I19" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1095,7 +1095,7 @@
         <v>หญิง</v>
       </c>
       <c r="I20" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1130,7 +1130,7 @@
         <v>หญิง</v>
       </c>
       <c r="I21" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1165,7 +1165,7 @@
         <v>ชาย</v>
       </c>
       <c r="I22" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v>ชาย</v>
       </c>
       <c r="I23" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1235,7 +1235,7 @@
         <v>ชาย</v>
       </c>
       <c r="I24" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1270,7 +1270,7 @@
         <v>ชาย</v>
       </c>
       <c r="I25" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -1305,7 +1305,7 @@
         <v>หญิง</v>
       </c>
       <c r="I26" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1340,7 +1340,7 @@
         <v>หญิง</v>
       </c>
       <c r="I27" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -1375,7 +1375,7 @@
         <v>หญิง</v>
       </c>
       <c r="I28" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1410,7 +1410,7 @@
         <v>ชาย</v>
       </c>
       <c r="I29" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -1445,7 +1445,7 @@
         <v>ชาย</v>
       </c>
       <c r="I30" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1480,7 +1480,7 @@
         <v>ชาย</v>
       </c>
       <c r="I31" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1515,7 +1515,7 @@
         <v>หญิง</v>
       </c>
       <c r="I32" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1550,7 +1550,7 @@
         <v>หญิง</v>
       </c>
       <c r="I33" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>หญิง</v>
       </c>
       <c r="I34" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1620,7 +1620,7 @@
         <v>หญิง</v>
       </c>
       <c r="I35" t="str">
-        <v>วอลเลย์บอล, สแตนเชียร์</v>
+        <v>วอลเลย์บอล, ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>ชาย</v>
       </c>
       <c r="I36" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1690,7 +1690,7 @@
         <v>ชาย</v>
       </c>
       <c r="I37" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1725,7 +1725,7 @@
         <v>ชาย</v>
       </c>
       <c r="I38" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1760,7 +1760,7 @@
         <v>ชาย</v>
       </c>
       <c r="I39" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -1795,7 +1795,7 @@
         <v>หญิง</v>
       </c>
       <c r="I40" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -1830,7 +1830,7 @@
         <v>หญิง</v>
       </c>
       <c r="I41" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -1865,7 +1865,7 @@
         <v>หญิง</v>
       </c>
       <c r="I42" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -1900,7 +1900,7 @@
         <v>ชาย</v>
       </c>
       <c r="I43" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -1935,7 +1935,7 @@
         <v>ชาย</v>
       </c>
       <c r="I44" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -1970,7 +1970,7 @@
         <v>ชาย</v>
       </c>
       <c r="I45" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2005,7 +2005,7 @@
         <v>หญิง</v>
       </c>
       <c r="I46" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2040,7 +2040,7 @@
         <v>หญิง</v>
       </c>
       <c r="I47" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2075,7 +2075,7 @@
         <v>หญิง</v>
       </c>
       <c r="I48" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2110,7 +2110,7 @@
         <v>หญิง</v>
       </c>
       <c r="I49" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -2145,7 +2145,7 @@
         <v>ชาย</v>
       </c>
       <c r="I50" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -2180,7 +2180,7 @@
         <v>ชาย</v>
       </c>
       <c r="I51" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2215,7 +2215,7 @@
         <v>ชาย</v>
       </c>
       <c r="I52" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2250,7 +2250,7 @@
         <v>ชาย</v>
       </c>
       <c r="I53" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J53" t="str">
         <v/>
@@ -2285,7 +2285,7 @@
         <v>หญิง</v>
       </c>
       <c r="I54" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J54" t="str">
         <v/>
@@ -2320,7 +2320,7 @@
         <v>หญิง</v>
       </c>
       <c r="I55" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2355,7 +2355,7 @@
         <v>หญิง</v>
       </c>
       <c r="I56" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -2390,7 +2390,7 @@
         <v>ชาย</v>
       </c>
       <c r="I57" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -2425,7 +2425,7 @@
         <v>ชาย</v>
       </c>
       <c r="I58" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -2460,7 +2460,7 @@
         <v>หญิง</v>
       </c>
       <c r="I59" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J59" t="str">
         <v/>
@@ -2495,7 +2495,7 @@
         <v>หญิง</v>
       </c>
       <c r="I60" t="str">
-        <v>สแตนเชียร์, เชียร์ลีดเดอร์</v>
+        <v>ฝ่ายสแตนเชียร์, ฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -2530,7 +2530,7 @@
         <v>หญิง</v>
       </c>
       <c r="I61" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -2565,7 +2565,7 @@
         <v>หญิง</v>
       </c>
       <c r="I62" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -2600,7 +2600,7 @@
         <v>ชาย</v>
       </c>
       <c r="I63" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -2635,7 +2635,7 @@
         <v>ชาย</v>
       </c>
       <c r="I64" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -2670,7 +2670,7 @@
         <v>ชาย</v>
       </c>
       <c r="I65" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -2705,7 +2705,7 @@
         <v>ชาย</v>
       </c>
       <c r="I66" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -2740,7 +2740,7 @@
         <v>หญิง</v>
       </c>
       <c r="I67" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -2775,7 +2775,7 @@
         <v>ชาย</v>
       </c>
       <c r="I68" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -2810,7 +2810,7 @@
         <v>ชาย</v>
       </c>
       <c r="I69" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -2845,7 +2845,7 @@
         <v>ชาย</v>
       </c>
       <c r="I70" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -2880,7 +2880,7 @@
         <v>หญิง</v>
       </c>
       <c r="I71" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>หญิง</v>
       </c>
       <c r="I72" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -2950,7 +2950,7 @@
         <v>ชาย</v>
       </c>
       <c r="I73" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>ชาย</v>
       </c>
       <c r="I74" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -3020,7 +3020,7 @@
         <v>ชาย</v>
       </c>
       <c r="I75" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -3055,7 +3055,7 @@
         <v>หญิง</v>
       </c>
       <c r="I76" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
         <v>หญิง</v>
       </c>
       <c r="I77" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -3125,7 +3125,7 @@
         <v>ชาย</v>
       </c>
       <c r="I78" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -3160,7 +3160,7 @@
         <v>ชาย</v>
       </c>
       <c r="I79" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -3195,7 +3195,7 @@
         <v>หญิง</v>
       </c>
       <c r="I80" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -3230,7 +3230,7 @@
         <v>หญิง</v>
       </c>
       <c r="I81" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -3265,7 +3265,7 @@
         <v>หญิง</v>
       </c>
       <c r="I82" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -3300,7 +3300,7 @@
         <v>ชาย</v>
       </c>
       <c r="I83" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J83" t="str">
         <v/>
@@ -3335,7 +3335,7 @@
         <v>ชาย</v>
       </c>
       <c r="I84" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -3370,7 +3370,7 @@
         <v>หญิง</v>
       </c>
       <c r="I85" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J85" t="str">
         <v/>
@@ -3405,7 +3405,7 @@
         <v>หญิง</v>
       </c>
       <c r="I86" t="str">
-        <v>สแตนเชียร์</v>
+        <v>ฝ่ายสแตนเชียร์</v>
       </c>
       <c r="J86" t="str">
         <v/>
@@ -3591,7 +3591,7 @@
         <v>หญิง</v>
       </c>
       <c r="I5" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J5" t="str">
         <v>092-376-2675</v>
@@ -3626,7 +3626,7 @@
         <v>หญิง</v>
       </c>
       <c r="I6" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J6" t="str">
         <v>095-191-5990</v>
@@ -3696,7 +3696,7 @@
         <v>หญิง</v>
       </c>
       <c r="I8" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J8" t="str">
         <v>095-135-9335</v>
@@ -4116,7 +4116,7 @@
         <v>หญิง</v>
       </c>
       <c r="I20" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J20" t="str">
         <v>082-594-4531</v>
@@ -4151,7 +4151,7 @@
         <v>หญิง</v>
       </c>
       <c r="I21" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J21" t="str">
         <v>099-272-6458</v>
@@ -4606,7 +4606,7 @@
         <v>หญิง</v>
       </c>
       <c r="I34" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J34" t="str">
         <v>096-104-0004</v>
@@ -4886,7 +4886,7 @@
         <v>หญิง</v>
       </c>
       <c r="I42" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J42" t="str">
         <v>061-314-0692</v>
@@ -5306,7 +5306,7 @@
         <v>หญิง</v>
       </c>
       <c r="I54" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J54" t="str">
         <v>082-119-4569</v>
@@ -5376,7 +5376,7 @@
         <v>หญิง</v>
       </c>
       <c r="I56" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J56" t="str">
         <v>095-796-7899</v>
@@ -5411,7 +5411,7 @@
         <v>หญิง</v>
       </c>
       <c r="I57" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J57" t="str">
         <v>097-145-3589</v>
@@ -5481,7 +5481,7 @@
         <v>ชาย</v>
       </c>
       <c r="I59" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J59" t="str">
         <v>095-357-2991</v>
@@ -5551,7 +5551,7 @@
         <v>หญิง</v>
       </c>
       <c r="I61" t="str">
-        <v>ฟุตบอล, ขบวนพาเหรด</v>
+        <v>ฟุตบอล, ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J61" t="str">
         <v>091-030-4248</v>
@@ -5586,7 +5586,7 @@
         <v>หญิง</v>
       </c>
       <c r="I62" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J62" t="str">
         <v>094-006-5719</v>
@@ -5796,7 +5796,7 @@
         <v>ชาย</v>
       </c>
       <c r="I68" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J68" t="str">
         <v>096-962-5615</v>
@@ -5831,7 +5831,7 @@
         <v>ชาย</v>
       </c>
       <c r="I69" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J69" t="str">
         <v>084-967-9146</v>
@@ -5866,7 +5866,7 @@
         <v>หญิง</v>
       </c>
       <c r="I70" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J70" t="str">
         <v>098-819-6918</v>
@@ -5901,7 +5901,7 @@
         <v>หญิง</v>
       </c>
       <c r="I71" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J71" t="str">
         <v>082-591-2812</v>
@@ -5971,7 +5971,7 @@
         <v>ชาย</v>
       </c>
       <c r="I73" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J73" t="str">
         <v>096-765-6020</v>
@@ -6041,7 +6041,7 @@
         <v>ชาย</v>
       </c>
       <c r="I75" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -6076,7 +6076,7 @@
         <v>หญิง</v>
       </c>
       <c r="I76" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J76" t="str">
         <v>098-384-5253</v>
@@ -6111,7 +6111,7 @@
         <v>หญิง</v>
       </c>
       <c r="I77" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J77" t="str">
         <v>064-326-1595</v>
@@ -6472,7 +6472,7 @@
         <v>หญิง</v>
       </c>
       <c r="I6" t="str">
-        <v>ดรัมเมเยอร์</v>
+        <v>ฝ่ายดรัมเมเยอร์</v>
       </c>
       <c r="J6" t="str">
         <v>099-616-9767</v>
@@ -6577,7 +6577,7 @@
         <v>หญิง</v>
       </c>
       <c r="I9" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J9" t="str">
         <v>091-049-3472</v>
@@ -6752,7 +6752,7 @@
         <v>หญิง</v>
       </c>
       <c r="I14" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J14" t="str">
         <v>083-097-3532</v>
@@ -6822,7 +6822,7 @@
         <v>หญิง</v>
       </c>
       <c r="I16" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J16" t="str">
         <v>099-738-2345</v>
@@ -6857,7 +6857,7 @@
         <v>หญิง</v>
       </c>
       <c r="I17" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J17" t="str">
         <v>098-738-9760</v>
@@ -6997,7 +6997,7 @@
         <v>หญิง</v>
       </c>
       <c r="I21" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J21" t="str">
         <v>096-294-5586</v>
@@ -7207,7 +7207,7 @@
         <v>หญิง</v>
       </c>
       <c r="I27" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J27" t="str">
         <v>082-965-5881</v>
@@ -7242,7 +7242,7 @@
         <v>หญิง</v>
       </c>
       <c r="I28" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J28" t="str">
         <v>083-097-3619</v>
@@ -7522,7 +7522,7 @@
         <v>หญิง</v>
       </c>
       <c r="I36" t="str">
-        <v>ดรัมเมเยอร์</v>
+        <v>ฝ่ายดรัมเมเยอร์</v>
       </c>
       <c r="J36" t="str">
         <v>085-849-9682</v>
@@ -7557,7 +7557,7 @@
         <v>หญิง</v>
       </c>
       <c r="I37" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J37" t="str">
         <v>063-019-1154</v>
@@ -7592,7 +7592,7 @@
         <v>หญิง</v>
       </c>
       <c r="I38" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J38" t="str">
         <v>098-689-7527</v>
@@ -7627,7 +7627,7 @@
         <v>หญิง</v>
       </c>
       <c r="I39" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J39" t="str">
         <v>065-250-6293</v>
@@ -7802,7 +7802,7 @@
         <v>หญิง</v>
       </c>
       <c r="I44" t="str">
-        <v>ดรัมเมเยอร์, ฟุตบอล</v>
+        <v>ฝ่ายดรัมเมเยอร์, ฟุตบอล</v>
       </c>
       <c r="J44" t="str">
         <v>080-800-6634</v>
@@ -7837,7 +7837,7 @@
         <v>หญิง</v>
       </c>
       <c r="I45" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J45" t="str">
         <v>062-226-3633</v>
@@ -8222,7 +8222,7 @@
         <v>หญิง</v>
       </c>
       <c r="I56" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J56" t="str">
         <v>095-358-9547</v>
@@ -8502,7 +8502,7 @@
         <v>หญิง</v>
       </c>
       <c r="I64" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J64" t="str">
         <v>065-975-1810</v>
@@ -8642,7 +8642,7 @@
         <v>หญิง</v>
       </c>
       <c r="I68" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J68" t="str">
         <v>096-084-2669</v>
@@ -8677,7 +8677,7 @@
         <v>หญิง</v>
       </c>
       <c r="I69" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J69" t="str">
         <v>080-137-4426</v>
@@ -8817,7 +8817,7 @@
         <v>หญิง</v>
       </c>
       <c r="I73" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J73" t="str">
         <v>098-951-4742</v>
@@ -8957,7 +8957,7 @@
         <v>หญิง</v>
       </c>
       <c r="I77" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J77" t="str">
         <v>092-825-3690</v>
@@ -9353,7 +9353,7 @@
         <v>หญิง</v>
       </c>
       <c r="I5" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J5" t="str">
         <v>090-494-0960</v>
@@ -9563,7 +9563,7 @@
         <v>หญิง</v>
       </c>
       <c r="I11" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J11" t="str">
         <v>083-337-9454</v>
@@ -9633,7 +9633,7 @@
         <v>หญิง</v>
       </c>
       <c r="I13" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J13" t="str">
         <v>061-230-7804</v>
@@ -9913,7 +9913,7 @@
         <v>หญิง</v>
       </c>
       <c r="I21" t="str">
-        <v>สวัสดิการ</v>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J21" t="str">
         <v>098-463-4302</v>
@@ -10088,7 +10088,7 @@
         <v>หญิง</v>
       </c>
       <c r="I26" t="str">
-        <v>ฝ่ายเชียร์ลีดเดอร์, ขบวนพาเหรด</v>
+        <v>ฝ่ายเชียร์ลีดเดอร์, ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J26" t="str">
         <v>062-514-6471</v>
@@ -10123,7 +10123,7 @@
         <v>หญิง</v>
       </c>
       <c r="I27" t="str">
-        <v>สวัสดิการ</v>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J27" t="str">
         <v>061-193-3676</v>
@@ -10298,7 +10298,7 @@
         <v>หญิง</v>
       </c>
       <c r="I32" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J32" t="str">
         <v>092-445-8482</v>
@@ -10403,7 +10403,7 @@
         <v>ชาย</v>
       </c>
       <c r="I35" t="str">
-        <v>สวัสดิการ</v>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J35" t="str">
         <v>064-326-0371</v>
@@ -10438,7 +10438,7 @@
         <v>ชาย</v>
       </c>
       <c r="I36" t="str">
-        <v>สวัสดิการ</v>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J36" t="str">
         <v>062-479-0695</v>
@@ -10473,7 +10473,7 @@
         <v>หญิง</v>
       </c>
       <c r="I37" t="str">
-        <v>สวัสดิการ</v>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J37" t="str">
         <v>065-837-6263</v>
@@ -10508,7 +10508,7 @@
         <v>หญิง</v>
       </c>
       <c r="I38" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J38" t="str">
         <v>098-269-0466</v>
@@ -10543,7 +10543,7 @@
         <v>หญิง</v>
       </c>
       <c r="I39" t="str">
-        <v>สวัสดิการ</v>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J39" t="str">
         <v>060-373-1209</v>
@@ -10613,7 +10613,7 @@
         <v>หญิง</v>
       </c>
       <c r="I41" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J41" t="str">
         <v>099-172-8992</v>
@@ -10788,7 +10788,7 @@
         <v>หญิง</v>
       </c>
       <c r="I46" t="str">
-        <v>สวัสดิการ</v>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J46" t="str">
         <v>083-799-7780</v>
@@ -10823,7 +10823,7 @@
         <v>หญิง</v>
       </c>
       <c r="I47" t="str">
-        <v>สวัสดิการ, วอลเลย์บอล, วิ่ง 16 ขา</v>
+        <v>ฝ่ายสวัสดิการ, วอลเลย์บอล, วิ่ง 16 ขา</v>
       </c>
       <c r="J47" t="str">
         <v>091-046-2589</v>
@@ -11068,7 +11068,7 @@
         <v>หญิง</v>
       </c>
       <c r="I54" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J54" t="str">
         <v>083-852-0626</v>
@@ -11208,7 +11208,7 @@
         <v>หญิง</v>
       </c>
       <c r="I58" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J58" t="str">
         <v>061-160-2991</v>
@@ -11628,7 +11628,7 @@
         <v>หญิง</v>
       </c>
       <c r="I70" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J70" t="str">
         <v>082-906-9603</v>
@@ -11663,7 +11663,7 @@
         <v>หญิง</v>
       </c>
       <c r="I71" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J71" t="str">
         <v>095-682-6677</v>
@@ -11698,7 +11698,7 @@
         <v>ชาย</v>
       </c>
       <c r="I72" t="str">
-        <v>วิ่ง 16 ขา, ขบวนพาเหรด</v>
+        <v>วิ่ง 16 ขา, ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J72" t="str">
         <v>096-663-3965</v>
@@ -11733,7 +11733,7 @@
         <v>ชาย</v>
       </c>
       <c r="I73" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J73" t="str">
         <v>096-664-4036</v>
@@ -11768,7 +11768,7 @@
         <v>ชาย</v>
       </c>
       <c r="I74" t="str">
-        <v>วิ่ง 16 ขา, ขบวนพาเหรด</v>
+        <v>วิ่ง 16 ขา, ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J74" t="str">
         <v>093-952-7843</v>
@@ -11803,7 +11803,7 @@
         <v>หญิง</v>
       </c>
       <c r="I75" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J75" t="str">
         <v>092-506-8497</v>
@@ -11838,7 +11838,7 @@
         <v>หญิง</v>
       </c>
       <c r="I76" t="str">
-        <v>ขบวนพาเหรด</v>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J76" t="str">
         <v>084-167-2074</v>
@@ -11943,7 +11943,7 @@
         <v>หญิง</v>
       </c>
       <c r="I79" t="str">
-        <v>ดรัมเมเยอร์</v>
+        <v>ฝ่ายดรัมเมเยอร์</v>
       </c>
       <c r="J79" t="str">
         <v>098-817-0691</v>
@@ -11978,7 +11978,7 @@
         <v>หญิง</v>
       </c>
       <c r="I80" t="str">
-        <v>ดรัมเมเยอร์</v>
+        <v>ฝ่ายดรัมเมเยอร์</v>
       </c>
       <c r="J80" t="str">
         <v>096-359-4382</v>
@@ -12118,7 +12118,7 @@
         <v>หญิง</v>
       </c>
       <c r="I84" t="str">
-        <v>อุปกรณ์และพร็อพ</v>
+        <v>ฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J84" t="str">
         <v>083-219-5152</v>
@@ -12339,7 +12339,7 @@
         <v>หญิง</v>
       </c>
       <c r="I5" t="str">
-        <v>สตาฟขบวนพาเหรด</v>
+        <v>สตาฟฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J5" t="str">
         <v>097-219-3314</v>
@@ -12409,7 +12409,7 @@
         <v>หญิง</v>
       </c>
       <c r="I7" t="str">
-        <v>คัลเลอร์การ์ด</v>
+        <v>ฝ่ายคัลเลอร์การ์ด</v>
       </c>
       <c r="J7" t="str">
         <v>063-786-4656</v>
@@ -12479,7 +12479,7 @@
         <v>ชาย</v>
       </c>
       <c r="I9" t="str">
-        <v>สตาฟอุปกรณ์และพร็อพ</v>
+        <v>สตาฟฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J9" t="str">
         <v>063-891-3857</v>
@@ -12549,7 +12549,7 @@
         <v>หญิง</v>
       </c>
       <c r="I11" t="str">
-        <v>สตาฟกองเชียร์</v>
+        <v>สตาฟฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J11" t="str">
         <v>062-220-7959</v>
@@ -12584,7 +12584,7 @@
         <v>หญิง</v>
       </c>
       <c r="I12" t="str">
-        <v>สตาฟกองเชียร์</v>
+        <v>สตาฟฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J12" t="str">
         <v>063-546-8896</v>
@@ -12689,7 +12689,7 @@
         <v>หญิง</v>
       </c>
       <c r="I15" t="str">
-        <v>สตาฟอุปกรณ์และพร็อพ</v>
+        <v>สตาฟฝ่ายอุปกรณ์และพร็อพ</v>
       </c>
       <c r="J15" t="str">
         <v>061-283-2615</v>
@@ -12864,7 +12864,7 @@
         <v>หญิง</v>
       </c>
       <c r="I20" t="str">
-        <v>สตาฟเชียร์ลีดเดอร์</v>
+        <v>สตาฟฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J20" t="str">
         <v>064-560-7577</v>
@@ -12934,7 +12934,7 @@
         <v>หญิง</v>
       </c>
       <c r="I22" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J22" t="str">
         <v>081-160-6764</v>
@@ -13109,7 +13109,7 @@
         <v>หญิง</v>
       </c>
       <c r="I27" t="str">
-        <v>ฟุตบอล, ดรัมเมเยอร์</v>
+        <v>ฟุตบอล, ฝ่ายดรัมเมเยอร์</v>
       </c>
       <c r="J27" t="str">
         <v>061-553-0691</v>
@@ -13144,7 +13144,7 @@
         <v>หญิง</v>
       </c>
       <c r="I28" t="str">
-        <v>ฟุตบอล, ดรัมเมเยอร์</v>
+        <v>ฟุตบอล, ฝ่ายดรัมเมเยอร์</v>
       </c>
       <c r="J28" t="str">
         <v>080-887-7109</v>
@@ -13214,7 +13214,7 @@
         <v>หญิง</v>
       </c>
       <c r="I30" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J30" t="str">
         <v>099-237-8944</v>
@@ -13249,7 +13249,7 @@
         <v>หญิง</v>
       </c>
       <c r="I31" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J31" t="str">
         <v>095-658-9660</v>
@@ -13424,7 +13424,7 @@
         <v>หญิง</v>
       </c>
       <c r="I36" t="str">
-        <v>หัวหน้าฝ่ายกองเชียร์</v>
+        <v>หัวหน้าฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J36" t="str">
         <v>065-493-0315</v>
@@ -13459,7 +13459,7 @@
         <v>หญิง</v>
       </c>
       <c r="I37" t="str">
-        <v>สตาฟขบวนพาเหรด</v>
+        <v>สตาฟฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -13494,7 +13494,7 @@
         <v>หญิง</v>
       </c>
       <c r="I38" t="str">
-        <v>หัวหน้าฝ่ายกองเชียร์</v>
+        <v>หัวหน้าฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J38" t="str">
         <v>083-884-2697</v>
@@ -13599,7 +13599,7 @@
         <v>หญิง</v>
       </c>
       <c r="I41" t="str">
-        <v>สตาฟเชียร์ลีดเดอร์</v>
+        <v>สตาฟฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J41" t="str">
         <v>080-736-1039</v>
@@ -13669,7 +13669,7 @@
         <v>หญิง</v>
       </c>
       <c r="I43" t="str">
-        <v>ดรัมเมเยอร์</v>
+        <v>ฝ่ายดรัมเมเยอร์</v>
       </c>
       <c r="J43" t="str">
         <v>099-263-2316</v>
@@ -13739,7 +13739,7 @@
         <v>หญิง</v>
       </c>
       <c r="I45" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J45" t="str">
         <v>065-678-3202</v>
@@ -13844,7 +13844,7 @@
         <v>หญิง</v>
       </c>
       <c r="I48" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J48" t="str">
         <v>065-291-7532</v>
@@ -13914,7 +13914,7 @@
         <v>หญิง</v>
       </c>
       <c r="I50" t="str">
-        <v>คัลเลอร์การ์ด</v>
+        <v>ฝ่ายคัลเลอร์การ์ด</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -14019,7 +14019,7 @@
         <v>ชาย</v>
       </c>
       <c r="I53" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J53" t="str">
         <v>082-035-6213</v>
@@ -14194,7 +14194,7 @@
         <v>หญิง</v>
       </c>
       <c r="I58" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J58" t="str">
         <v>064-869-4386</v>
@@ -14264,7 +14264,7 @@
         <v>หญิง</v>
       </c>
       <c r="I60" t="str">
-        <v>สตาฟกองเชียร์</v>
+        <v>สตาฟฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J60" t="str">
         <v>065-687-9600</v>
@@ -14334,7 +14334,7 @@
         <v>หญิง</v>
       </c>
       <c r="I62" t="str">
-        <v>สตาฟกองเชียร์</v>
+        <v>สตาฟฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J62" t="str">
         <v>083-025-2578</v>
@@ -14544,7 +14544,7 @@
         <v>ชาย</v>
       </c>
       <c r="I68" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J68" t="str">
         <v>080-825-7625</v>
@@ -14719,7 +14719,7 @@
         <v>ชาย</v>
       </c>
       <c r="I73" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J73" t="str">
         <v/>
@@ -14929,7 +14929,7 @@
         <v>ชาย</v>
       </c>
       <c r="I79" t="str">
-        <v>สตาฟสวัสดิการ</v>
+        <v>สตาฟฝ่ายสวัสดิการ</v>
       </c>
       <c r="J79" t="str">
         <v>091-969-6155</v>
@@ -14999,7 +14999,7 @@
         <v>หญิง</v>
       </c>
       <c r="I81" t="str">
-        <v>คัลเลอร์การ์ด</v>
+        <v>ฝ่ายคัลเลอร์การ์ด</v>
       </c>
       <c r="J81" t="str">
         <v/>

--- a/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
+++ b/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
@@ -6425,16 +6425,16 @@
         <v>ม.3/1</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F5" t="str">
-        <v>34049</v>
+        <v>33629</v>
       </c>
       <c r="G5" t="str">
-        <v>เด็กหญิงพชรพร รอดสุด</v>
+        <v>นายวีรภัทร มูลชัย</v>
       </c>
       <c r="H5" t="str">
-        <v>หญิง</v>
+        <v>ชาย</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -15138,16 +15138,16 @@
         <v>ม.6/1</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F4" t="str">
-        <v>32128</v>
+        <v>32138</v>
       </c>
       <c r="G4" t="str">
-        <v>นายภูมินทร์ หลวงแสง</v>
+        <v>นางสาวธนาภรณ์ ไชยเมืองชื่น</v>
       </c>
       <c r="H4" t="str">
-        <v>ชาย</v>
+        <v>หญิง</v>
       </c>
       <c r="I4" t="str">
         <v/>

--- a/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
+++ b/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
@@ -3661,10 +3661,10 @@
         <v>หญิง</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>เปตอง</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>098-567-1827</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -3766,10 +3766,10 @@
         <v>ชาย</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>080-747-3184</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>หญิง</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>095-389-8605</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -3871,7 +3871,7 @@
         <v>หญิง</v>
       </c>
       <c r="I13" t="str">
-        <v>วอลเลย์บอล</v>
+        <v>วอลเลย์บอล, ฟุตบอล</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>หญิง</v>
       </c>
       <c r="I15" t="str">
-        <v>วอลเลย์บอล</v>
+        <v>วอลเลย์บอล, ฟุตบอล</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -4361,10 +4361,10 @@
         <v>หญิง</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>064-251-9806</v>
       </c>
       <c r="K27" t="str">
         <v/>
@@ -4396,10 +4396,10 @@
         <v>หญิง</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>083-451-7140</v>
       </c>
       <c r="K28" t="str">
         <v/>
@@ -4431,10 +4431,10 @@
         <v>หญิง</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>065-858-8204</v>
       </c>
       <c r="K29" t="str">
         <v/>
@@ -4641,10 +4641,10 @@
         <v>หญิง</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>คัลเลอร์การ์ด</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>093-243-6307</v>
       </c>
       <c r="K35" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
       <c r="D36" t="str">
         <v>ม.2/5</v>
       </c>
-      <c r="E36" t="str">
+      <c r="E36">
         <v>-</v>
       </c>
       <c r="F36" t="str">
@@ -4851,10 +4851,10 @@
         <v>หญิง</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>ฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>093-393-1626</v>
       </c>
       <c r="K41" t="str">
         <v/>
@@ -4921,10 +4921,10 @@
         <v>ชาย</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>ฝ่ายพร็อพ</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>091-027-7059</v>
       </c>
       <c r="K43" t="str">
         <v/>
@@ -5026,10 +5026,10 @@
         <v>หญิง</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>ฝ่ายคัลเลอร์การ์ด</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>091-024-8039</v>
       </c>
       <c r="K46" t="str">
         <v/>
@@ -5131,10 +5131,10 @@
         <v>หญิง</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>คัลเลอร์การ์ด</v>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>065-379-1693</v>
       </c>
       <c r="K49" t="str">
         <v/>
@@ -5236,10 +5236,10 @@
         <v>ชาย</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>080-854-1169</v>
       </c>
       <c r="K52" t="str">
         <v/>
@@ -5341,10 +5341,10 @@
         <v>หญิง</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>ฝ่ายเชียร์ลีดเดอร์</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>061-794-0872</v>
       </c>
       <c r="K55" t="str">
         <v/>
@@ -5446,10 +5446,10 @@
         <v>ชาย</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>081-077-9340</v>
       </c>
       <c r="K58" t="str">
         <v/>
@@ -6507,10 +6507,10 @@
         <v>หญิง</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>096-682-1854</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -6542,10 +6542,10 @@
         <v>หญิง</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>084-017-6210</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -7032,7 +7032,7 @@
         <v>หญิง</v>
       </c>
       <c r="I22" t="str">
-        <v>ฟุตบอล</v>
+        <v>ฟุตบอล, กรีฑา, บาสเกตบอล</v>
       </c>
       <c r="J22" t="str">
         <v>061-983-7797</v>
@@ -7697,10 +7697,10 @@
         <v>ชาย</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>กรีฑา</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>061-439-7907</v>
       </c>
       <c r="K41" t="str">
         <v/>
@@ -7732,10 +7732,10 @@
         <v>หญิง</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>092-452-1062</v>
       </c>
       <c r="K42" t="str">
         <v/>
@@ -7767,7 +7767,7 @@
         <v>หญิง</v>
       </c>
       <c r="I43" t="str">
-        <v>ฟุตบอล</v>
+        <v>ฟุตบอล, กรีฑา, บาสเกตบอล</v>
       </c>
       <c r="J43" t="str">
         <v>093-131-8108</v>
@@ -8047,10 +8047,10 @@
         <v>หญิง</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>082-086-7639</v>
       </c>
       <c r="K51" t="str">
         <v/>
@@ -8747,10 +8747,10 @@
         <v>ชาย</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>ฟุตบอล</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>061-150-8435</v>
       </c>
       <c r="K71" t="str">
         <v/>
@@ -9388,10 +9388,10 @@
         <v>หญิง</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>ฝ่ายพร็อพ</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>088-599-5886</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -9423,10 +9423,10 @@
         <v>หญิง</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>ฝ่ายพร็อพ</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>063-035-2452</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -9843,10 +9843,10 @@
         <v>หญิง</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>084-049-5162</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -9878,10 +9878,10 @@
         <v>หญิง</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>ฝ่ายพร็อพ</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>063-751-0224</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -9948,10 +9948,10 @@
         <v>ชาย</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>062-120-5203</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -10053,10 +10053,10 @@
         <v>หญิง</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>คัลเลอร์การ์ด, ฝ่ายคัลเลอร์การ์ด</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>065-484-2530</v>
       </c>
       <c r="K25" t="str">
         <v/>
@@ -10158,10 +10158,10 @@
         <v>ชาย</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>064-591-4070</v>
       </c>
       <c r="K28" t="str">
         <v/>
@@ -10228,10 +10228,10 @@
         <v>ชาย</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>วิ่ง 16 ขา</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>099-435-6995</v>
       </c>
       <c r="K30" t="str">
         <v/>
@@ -10263,10 +10263,10 @@
         <v>หญิง</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>คัลเลอร์การ์ด</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>094-920-3178</v>
       </c>
       <c r="K31" t="str">
         <v/>
@@ -10648,10 +10648,10 @@
         <v>ชาย</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>095-602-8523</v>
       </c>
       <c r="K42" t="str">
         <v/>
@@ -10718,10 +10718,10 @@
         <v>หญิง</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>ฟุตบอล</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>099-193-7702</v>
       </c>
       <c r="K44" t="str">
         <v/>
@@ -10963,10 +10963,10 @@
         <v>ชาย</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>วิ่ง 16 ขา</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>083-214-0843</v>
       </c>
       <c r="K51" t="str">
         <v/>
@@ -11173,10 +11173,10 @@
         <v>หญิง</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>ฝ่ายพร็อพ</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>098-749-3595</v>
       </c>
       <c r="K57" t="str">
         <v/>
@@ -11265,7 +11265,7 @@
       <c r="D60" t="str">
         <v>ม.4/9</v>
       </c>
-      <c r="E60" t="str">
+      <c r="E60">
         <v>-</v>
       </c>
       <c r="F60" t="str">
@@ -11300,7 +11300,7 @@
       <c r="D61" t="str">
         <v>ม.4/9</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E61">
         <v>-</v>
       </c>
       <c r="F61" t="str">
@@ -11418,10 +11418,10 @@
         <v>หญิง</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J64" t="str">
-        <v/>
+        <v>093-132-7524</v>
       </c>
       <c r="K64" t="str">
         <v/>
@@ -11453,10 +11453,10 @@
         <v>หญิง</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J65" t="str">
-        <v/>
+        <v>095-635-3078</v>
       </c>
       <c r="K65" t="str">
         <v/>
@@ -11488,10 +11488,10 @@
         <v>หญิง</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>098-721-9619</v>
       </c>
       <c r="K66" t="str">
         <v/>
@@ -11558,10 +11558,10 @@
         <v>ชาย</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>ฝ่ายพร็อพ</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>084-050-3337</v>
       </c>
       <c r="K68" t="str">
         <v/>
@@ -11873,10 +11873,10 @@
         <v>ชาย</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J77" t="str">
-        <v/>
+        <v>061-269-5726</v>
       </c>
       <c r="K77" t="str">
         <v/>
@@ -11908,10 +11908,10 @@
         <v>ชาย</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>ฝ่ายสวัสดิการ</v>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>096-667-3887</v>
       </c>
       <c r="K78" t="str">
         <v/>
@@ -12013,7 +12013,7 @@
         <v>หญิง</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>คัลเลอร์การ์ด</v>
       </c>
       <c r="J81" t="str">
         <v/>
@@ -12724,7 +12724,7 @@
         <v>ชาย</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>กรีฑา</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -12956,7 +12956,7 @@
       <c r="D23" t="str">
         <v>ม.5/3</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E23">
         <v>-</v>
       </c>
       <c r="F23" t="str">
@@ -13354,10 +13354,10 @@
         <v>ชาย</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>สตาฟเปตอง</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>096-976-2786</v>
       </c>
       <c r="K34" t="str">
         <v/>
@@ -13879,10 +13879,10 @@
         <v>หญิง</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>สตาฟฝ่ายพร็อพ</v>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>666-207-6517</v>
       </c>
       <c r="K49" t="str">
         <v/>
@@ -13949,10 +13949,10 @@
         <v>หญิง</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>สตาฟฝ่ายพร็อพ</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>061-684-3615</v>
       </c>
       <c r="K51" t="str">
         <v/>
@@ -14054,10 +14054,10 @@
         <v>ชาย</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>สตาฟฝ่ายพร็อพ</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>083-214-8508</v>
       </c>
       <c r="K54" t="str">
         <v/>
@@ -14124,7 +14124,7 @@
         <v>หญิง</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>ขบวนพาเหรด</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -15605,10 +15605,10 @@
         <v>ชาย</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>บาสเกตบอล</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>082-590-6971</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -17495,10 +17495,10 @@
         <v>หญิง</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>ฝ่ายขบวนพาเหรด</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>097-021-8357</v>
       </c>
       <c r="K71" t="str">
         <v/>

--- a/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
+++ b/เอกสารและรายชื่อคณะสีแสด_ปี69/รายชื่อคณะสีแสด_ปี69.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4054" uniqueCount="1378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4054" uniqueCount="1391">
   <si>
     <t>รายชื่อนักเรียน คณะสีแสด (สีบุษราคัม) - ระดับชั้นมัธยมศึกษาปีที่ 1</t>
   </si>
@@ -1371,7 +1371,7 @@
     <t>รายชื่อนักเรียน คณะสีแสด (สีบุษราคัม) - ระดับชั้นมัธยมศึกษาปีที่ 3</t>
   </si>
   <si>
-    <t>จำนวนนักเรียน: 82 คน | ชาย: 29 คน | หญิง: 53 คน | ผู้มีหน้าที่/นักกีฬา/สตาฟ: 65 คน (เรียงตาม: ห้องเรียน -&gt; รหัสประจำตัว)</t>
+    <t>จำนวนนักเรียน: 82 คน | ชาย: 29 คน | หญิง: 53 คน | ผู้มีหน้าที่/นักกีฬา/สตาฟ: 68 คน (เรียงตาม: ห้องเรียน -&gt; รหัสประจำตัว)</t>
   </si>
   <si>
     <t>ม.3</t>
@@ -1602,6 +1602,12 @@
     <t>เด็กหญิงยิ่งรักษ์ อินไผ่</t>
   </si>
   <si>
+    <t>ฝ่ายพร็อพ</t>
+  </si>
+  <si>
+    <t>062-148-0398</t>
+  </si>
+  <si>
     <t>33773</t>
   </si>
   <si>
@@ -1614,6 +1620,9 @@
     <t>นางสาวสาวิตรี ลลิตาคม</t>
   </si>
   <si>
+    <t>094-818-4981</t>
+  </si>
+  <si>
     <t>ม.3/5</t>
   </si>
   <si>
@@ -1821,6 +1830,9 @@
     <t>เด็กหญิงเขมจิรา อินต๊ะ</t>
   </si>
   <si>
+    <t>064-065-9449</t>
+  </si>
+  <si>
     <t>33917</t>
   </si>
   <si>
@@ -2043,13 +2055,13 @@
     <t>รวมทั้งสิ้น ระดับชั้น ม.3</t>
   </si>
   <si>
-    <t>82 คน (ชาย 29 / หญิง 53 | ผู้มีหน้าที่ 65 คน)</t>
+    <t>82 คน (ชาย 29 / หญิง 53 | ผู้มีหน้าที่ 68 คน)</t>
   </si>
   <si>
     <t>รายชื่อนักเรียน คณะสีแสด (สีบุษราคัม) - ระดับชั้นมัธยมศึกษาปีที่ 4</t>
   </si>
   <si>
-    <t>จำนวนนักเรียน: 84 คน | ชาย: 38 คน | หญิง: 46 คน | ผู้มีหน้าที่/นักกีฬา/สตาฟ: 71 คน (เรียงตาม: ห้องเรียน -&gt; รหัสประจำตัว)</t>
+    <t>จำนวนนักเรียน: 84 คน | ชาย: 38 คน | หญิง: 46 คน | ผู้มีหน้าที่/นักกีฬา/สตาฟ: 72 คน (เรียงตาม: ห้องเรียน -&gt; รหัสประจำตัว)</t>
   </si>
   <si>
     <t>ม.4</t>
@@ -2094,6 +2106,9 @@
     <t>นายสิปปกร ศิริวงขันธ์</t>
   </si>
   <si>
+    <t>099-442-7467</t>
+  </si>
+  <si>
     <t>35401</t>
   </si>
   <si>
@@ -2112,6 +2127,9 @@
     <t>เด็กชายธนกฤต สุยะตุ่น</t>
   </si>
   <si>
+    <t>081-261-8553</t>
+  </si>
+  <si>
     <t>33168</t>
   </si>
   <si>
@@ -2211,7 +2229,10 @@
     <t>นางสาวศรัณย์พร ปากแบน</t>
   </si>
   <si>
-    <t>098-463-4302</t>
+    <t>สวัสดิการ, บาสเกตบอล</t>
+  </si>
+  <si>
+    <t>098-463-4502</t>
   </si>
   <si>
     <t>ม.4/4</t>
@@ -2298,6 +2319,9 @@
     <t>เด็กหญิงกวินธิดา อินธรรม</t>
   </si>
   <si>
+    <t>ขบวนพาเหรด, คัลเลอร์การ์ด</t>
+  </si>
+  <si>
     <t>092-445-8482</t>
   </si>
   <si>
@@ -2370,6 +2394,9 @@
     <t>เด็กหญิงรับพร คีรีตระหง่าน</t>
   </si>
   <si>
+    <t>สวัสดิการ, คัลเลอร์การ์ด</t>
+  </si>
+  <si>
     <t>060-373-1209</t>
   </si>
   <si>
@@ -2799,7 +2826,7 @@
     <t>รวมทั้งสิ้น ระดับชั้น ม.4</t>
   </si>
   <si>
-    <t>84 คน (ชาย 38 / หญิง 46 | ผู้มีหน้าที่ 71 คน)</t>
+    <t>84 คน (ชาย 38 / หญิง 46 | ผู้มีหน้าที่ 72 คน)</t>
   </si>
   <si>
     <t>รายชื่อนักเรียน คณะสีแสด (สีบุษราคัม) - ระดับชั้นมัธยมศึกษาปีที่ 5</t>
@@ -3021,102 +3048,105 @@
     <t>นางสาวเกศศิริประภา ใจมา</t>
   </si>
   <si>
+    <t>สตาฟสวัสดิการ, คัลเลอร์การ์ด</t>
+  </si>
+  <si>
+    <t>081-160-6764</t>
+  </si>
+  <si>
+    <t>34759</t>
+  </si>
+  <si>
+    <t>นายณัฐทวัฒน์ เอี้ยงหมี</t>
+  </si>
+  <si>
+    <t>ตะกร้อ</t>
+  </si>
+  <si>
+    <t>099-405-2582</t>
+  </si>
+  <si>
+    <t>34764</t>
+  </si>
+  <si>
+    <t>นางสาวณัฐธิดา กัณหา</t>
+  </si>
+  <si>
+    <t>ม.5/4</t>
+  </si>
+  <si>
+    <t>32449</t>
+  </si>
+  <si>
+    <t>นายอธิภู คำฟอง</t>
+  </si>
+  <si>
+    <t>สตาฟบาสเกตบอล</t>
+  </si>
+  <si>
+    <t>097-287-1024</t>
+  </si>
+  <si>
+    <t>32510</t>
+  </si>
+  <si>
+    <t>นางสาวศุภิสรา ตาแสงวงษ์</t>
+  </si>
+  <si>
+    <t>ฟุตบอล, ดรัมเมเยอร์</t>
+  </si>
+  <si>
+    <t>061-553-0691</t>
+  </si>
+  <si>
+    <t>32631</t>
+  </si>
+  <si>
+    <t>นางสาวสาริกา ปราณนคร</t>
+  </si>
+  <si>
+    <t>080-887-7109</t>
+  </si>
+  <si>
+    <t>32646</t>
+  </si>
+  <si>
+    <t>นายศักดิธัช จินตา</t>
+  </si>
+  <si>
+    <t>32757</t>
+  </si>
+  <si>
+    <t>นางสาวกานต์พิชชา พฤกษาพรรพต</t>
+  </si>
+  <si>
+    <t>ฟุตบอล, สตาฟฟุตบอลชาย</t>
+  </si>
+  <si>
+    <t>084-989-0044</t>
+  </si>
+  <si>
+    <t>34770</t>
+  </si>
+  <si>
+    <t>นายธนวัฒน์ อุดจอม</t>
+  </si>
+  <si>
+    <t>มือกลอง</t>
+  </si>
+  <si>
+    <t>063-113-6053</t>
+  </si>
+  <si>
+    <t>34776</t>
+  </si>
+  <si>
+    <t>นางสาววิภาดา แก้วตา</t>
+  </si>
+  <si>
     <t>สตาฟสวัสดิการ</t>
   </si>
   <si>
-    <t>081-160-6764</t>
-  </si>
-  <si>
-    <t>34759</t>
-  </si>
-  <si>
-    <t>นายณัฐทวัฒน์ เอี้ยงหมี</t>
-  </si>
-  <si>
-    <t>ตะกร้อ</t>
-  </si>
-  <si>
-    <t>099-405-2582</t>
-  </si>
-  <si>
-    <t>34764</t>
-  </si>
-  <si>
-    <t>นางสาวณัฐธิดา กัณหา</t>
-  </si>
-  <si>
-    <t>ม.5/4</t>
-  </si>
-  <si>
-    <t>32449</t>
-  </si>
-  <si>
-    <t>นายอธิภู คำฟอง</t>
-  </si>
-  <si>
-    <t>สตาฟบาสเกตบอล</t>
-  </si>
-  <si>
-    <t>097-287-1024</t>
-  </si>
-  <si>
-    <t>32510</t>
-  </si>
-  <si>
-    <t>นางสาวศุภิสรา ตาแสงวงษ์</t>
-  </si>
-  <si>
-    <t>ฟุตบอล, ดรัมเมเยอร์</t>
-  </si>
-  <si>
-    <t>061-553-0691</t>
-  </si>
-  <si>
-    <t>32631</t>
-  </si>
-  <si>
-    <t>นางสาวสาริกา ปราณนคร</t>
-  </si>
-  <si>
-    <t>080-887-7109</t>
-  </si>
-  <si>
-    <t>32646</t>
-  </si>
-  <si>
-    <t>นายศักดิธัช จินตา</t>
-  </si>
-  <si>
-    <t>32757</t>
-  </si>
-  <si>
-    <t>นางสาวกานต์พิชชา พฤกษาพรรพต</t>
-  </si>
-  <si>
-    <t>ฟุตบอล, สตาฟฟุตบอลชาย</t>
-  </si>
-  <si>
-    <t>084-989-0044</t>
-  </si>
-  <si>
-    <t>34770</t>
-  </si>
-  <si>
-    <t>นายธนวัฒน์ อุดจอม</t>
-  </si>
-  <si>
-    <t>มือกลอง</t>
-  </si>
-  <si>
-    <t>063-113-6053</t>
-  </si>
-  <si>
-    <t>34776</t>
-  </si>
-  <si>
-    <t>นางสาววิภาดา แก้วตา</t>
-  </si>
-  <si>
     <t>099-237-8944</t>
   </si>
   <si>
@@ -3540,6 +3570,12 @@
     <t>นายอิธิกุล โมเฮด</t>
   </si>
   <si>
+    <t>ฝ่ายสวัสดิการ</t>
+  </si>
+  <si>
+    <t>065-496-0745</t>
+  </si>
+  <si>
     <t>32795</t>
   </si>
   <si>
@@ -3553,6 +3589,9 @@
   </si>
   <si>
     <t>นายพีรพล ทวีทรัพย์ล้ำเลิศ</t>
+  </si>
+  <si>
+    <t>รองประธานคณะสีแสด, กรีฑา, เปตอง, ตะกร้อ, วอลเลย์บอล, บาสเกตบอล, ฟุตบอล, วิ่ง 16 ขา</t>
   </si>
   <si>
     <t>061-267-2452</t>
@@ -11012,7 +11051,7 @@
         <v>28</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>269</v>
+        <v>464</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>476</v>
@@ -11712,10 +11751,10 @@
         <v>28</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>19</v>
+        <v>528</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>19</v>
+        <v>529</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>19</v>
@@ -11738,10 +11777,10 @@
         <v>40</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>28</v>
@@ -11773,19 +11812,19 @@
         <v>43</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>19</v>
+        <v>534</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>19</v>
@@ -11802,16 +11841,16 @@
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E35" s="4">
         <v>4</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>17</v>
@@ -11837,16 +11876,16 @@
         <v>5</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E36" s="7">
         <v>10</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>17</v>
@@ -11872,16 +11911,16 @@
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E37" s="4">
         <v>16</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>17</v>
@@ -11890,7 +11929,7 @@
         <v>279</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>19</v>
@@ -11907,16 +11946,16 @@
         <v>5</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E38" s="7">
         <v>22</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>28</v>
@@ -11925,7 +11964,7 @@
         <v>218</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>19</v>
@@ -11942,16 +11981,16 @@
         <v>5</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E39" s="4">
         <v>28</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>28</v>
@@ -11960,7 +11999,7 @@
         <v>464</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>19</v>
@@ -11977,16 +12016,16 @@
         <v>5</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E40" s="7">
         <v>34</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>28</v>
@@ -11995,7 +12034,7 @@
         <v>269</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>19</v>
@@ -12012,16 +12051,16 @@
         <v>5</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E41" s="4">
         <v>40</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>28</v>
@@ -12030,7 +12069,7 @@
         <v>269</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>19</v>
@@ -12047,16 +12086,16 @@
         <v>5</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E42" s="7">
         <v>42</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>28</v>
@@ -12065,7 +12104,7 @@
         <v>269</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="K42" s="9" t="s">
         <v>19</v>
@@ -12082,16 +12121,16 @@
         <v>6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E43" s="4">
         <v>6</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>17</v>
@@ -12117,16 +12156,16 @@
         <v>6</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E44" s="7">
         <v>12</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>17</v>
@@ -12135,7 +12174,7 @@
         <v>214</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K44" s="9" t="s">
         <v>19</v>
@@ -12152,16 +12191,16 @@
         <v>6</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E45" s="4">
         <v>18</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>28</v>
@@ -12170,7 +12209,7 @@
         <v>224</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>19</v>
@@ -12187,16 +12226,16 @@
         <v>6</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E46" s="7">
         <v>24</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>28</v>
@@ -12205,7 +12244,7 @@
         <v>509</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>19</v>
@@ -12222,25 +12261,25 @@
         <v>6</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E47" s="4">
         <v>30</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>19</v>
@@ -12257,16 +12296,16 @@
         <v>6</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E48" s="7">
         <v>36</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>28</v>
@@ -12275,7 +12314,7 @@
         <v>224</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>19</v>
@@ -12292,16 +12331,16 @@
         <v>7</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E49" s="4">
         <v>2</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>17</v>
@@ -12327,16 +12366,16 @@
         <v>7</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E50" s="7">
         <v>7</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>17</v>
@@ -12345,7 +12384,7 @@
         <v>286</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K50" s="9" t="s">
         <v>19</v>
@@ -12362,16 +12401,16 @@
         <v>7</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E51" s="4">
         <v>15</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>28</v>
@@ -12380,7 +12419,7 @@
         <v>279</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>19</v>
@@ -12397,16 +12436,16 @@
         <v>7</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E52" s="7">
         <v>21</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>28</v>
@@ -12432,16 +12471,16 @@
         <v>7</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E53" s="4">
         <v>27</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>28</v>
@@ -12450,7 +12489,7 @@
         <v>224</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>19</v>
@@ -12467,16 +12506,16 @@
         <v>7</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E54" s="7">
         <v>33</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>28</v>
@@ -12485,7 +12524,7 @@
         <v>214</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>19</v>
@@ -12502,16 +12541,16 @@
         <v>7</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E55" s="4">
         <v>13</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>17</v>
@@ -12537,16 +12576,16 @@
         <v>8</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E56" s="7">
         <v>4</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>17</v>
@@ -12555,7 +12594,7 @@
         <v>279</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="K56" s="9" t="s">
         <v>19</v>
@@ -12572,16 +12611,16 @@
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E57" s="4">
         <v>10</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>17</v>
@@ -12607,25 +12646,25 @@
         <v>8</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E58" s="7">
         <v>16</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>19</v>
+        <v>528</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>19</v>
+        <v>604</v>
       </c>
       <c r="K58" s="9" t="s">
         <v>19</v>
@@ -12642,16 +12681,16 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E59" s="4">
         <v>22</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>28</v>
@@ -12660,7 +12699,7 @@
         <v>269</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>19</v>
@@ -12677,16 +12716,16 @@
         <v>8</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E60" s="7">
         <v>28</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>28</v>
@@ -12695,7 +12734,7 @@
         <v>214</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="K60" s="9" t="s">
         <v>19</v>
@@ -12712,16 +12751,16 @@
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E61" s="4">
         <v>34</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>28</v>
@@ -12730,7 +12769,7 @@
         <v>279</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>19</v>
@@ -12747,16 +12786,16 @@
         <v>8</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E62" s="7">
         <v>39</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>28</v>
@@ -12765,7 +12804,7 @@
         <v>214</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K62" s="9" t="s">
         <v>19</v>
@@ -12782,16 +12821,16 @@
         <v>9</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E63" s="4">
         <v>6</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>17</v>
@@ -12800,7 +12839,7 @@
         <v>221</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>19</v>
@@ -12817,16 +12856,16 @@
         <v>9</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E64" s="7">
         <v>12</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>17</v>
@@ -12852,16 +12891,16 @@
         <v>9</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E65" s="4">
         <v>18</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>28</v>
@@ -12887,16 +12926,16 @@
         <v>9</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E66" s="7">
         <v>24</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>28</v>
@@ -12922,16 +12961,16 @@
         <v>9</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E67" s="4">
         <v>30</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>28</v>
@@ -12940,7 +12979,7 @@
         <v>269</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>19</v>
@@ -12957,16 +12996,16 @@
         <v>10</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E68" s="7">
         <v>6</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>17</v>
@@ -12992,16 +13031,16 @@
         <v>10</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E69" s="4">
         <v>11</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>17</v>
@@ -13027,16 +13066,16 @@
         <v>10</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E70" s="7">
         <v>17</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>28</v>
@@ -13062,16 +13101,16 @@
         <v>10</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E71" s="4">
         <v>24</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>28</v>
@@ -13080,7 +13119,7 @@
         <v>224</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>19</v>
@@ -13097,16 +13136,16 @@
         <v>10</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E72" s="7">
         <v>30</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>28</v>
@@ -13115,7 +13154,7 @@
         <v>269</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K72" s="9" t="s">
         <v>19</v>
@@ -13132,16 +13171,16 @@
         <v>11</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E73" s="4">
         <v>6</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>17</v>
@@ -13150,7 +13189,7 @@
         <v>242</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>19</v>
@@ -13167,16 +13206,16 @@
         <v>11</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E74" s="7">
         <v>12</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>17</v>
@@ -13185,7 +13224,7 @@
         <v>218</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="K74" s="9" t="s">
         <v>19</v>
@@ -13202,16 +13241,16 @@
         <v>11</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E75" s="4">
         <v>18</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>28</v>
@@ -13237,16 +13276,16 @@
         <v>11</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E76" s="7">
         <v>24</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>28</v>
@@ -13255,7 +13294,7 @@
         <v>269</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K76" s="9" t="s">
         <v>19</v>
@@ -13272,16 +13311,16 @@
         <v>11</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E77" s="4">
         <v>29</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>28</v>
@@ -13307,16 +13346,16 @@
         <v>12</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E78" s="7">
         <v>6</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>17</v>
@@ -13342,16 +13381,16 @@
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E79" s="4">
         <v>12</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>28</v>
@@ -13377,16 +13416,16 @@
         <v>12</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E80" s="7">
         <v>18</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>28</v>
@@ -13395,7 +13434,7 @@
         <v>224</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K80" s="9" t="s">
         <v>19</v>
@@ -13412,7 +13451,7 @@
         <v>12</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E81" s="4">
         <v>24</v>
@@ -13447,16 +13486,16 @@
         <v>12</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E82" s="7">
         <v>30</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>28</v>
@@ -13482,16 +13521,16 @@
         <v>13</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E83" s="4">
         <v>4</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>17</v>
@@ -13517,16 +13556,16 @@
         <v>13</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E84" s="7">
         <v>10</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>17</v>
@@ -13552,16 +13591,16 @@
         <v>13</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E85" s="4">
         <v>16</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>28</v>
@@ -13570,7 +13609,7 @@
         <v>279</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>19</v>
@@ -13587,16 +13626,16 @@
         <v>13</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E86" s="7">
         <v>21</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>28</v>
@@ -13605,7 +13644,7 @@
         <v>218</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="K86" s="9" t="s">
         <v>19</v>
@@ -13613,7 +13652,7 @@
     </row>
     <row r="87" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
@@ -13621,7 +13660,7 @@
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="11" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="H87" s="12" t="s">
         <v>19</v>
@@ -13667,7 +13706,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13682,7 +13721,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13736,22 +13775,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E5" s="4">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>28</v>
@@ -13760,7 +13799,7 @@
         <v>224</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>19</v>
@@ -13771,22 +13810,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E6" s="7">
         <v>6</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>17</v>
@@ -13806,22 +13845,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E7" s="4">
         <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>28</v>
@@ -13830,7 +13869,7 @@
         <v>269</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>19</v>
@@ -13841,22 +13880,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E8" s="7">
         <v>12</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>17</v>
@@ -13876,22 +13915,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E9" s="4">
         <v>17</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>17</v>
@@ -13900,7 +13939,7 @@
         <v>218</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>19</v>
+        <v>696</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>19</v>
@@ -13911,22 +13950,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E10" s="7">
         <v>35</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>28</v>
@@ -13935,7 +13974,7 @@
         <v>269</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>19</v>
@@ -13946,31 +13985,31 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C11" s="4">
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>19</v>
+        <v>528</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>19</v>
+        <v>703</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>19</v>
@@ -13981,22 +14020,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C12" s="7">
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E12" s="7">
         <v>19</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>28</v>
@@ -14005,7 +14044,7 @@
         <v>224</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>19</v>
@@ -14016,31 +14055,31 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E13" s="4">
         <v>25</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>19</v>
@@ -14051,22 +14090,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C14" s="7">
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E14" s="7">
         <v>31</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>28</v>
@@ -14075,7 +14114,7 @@
         <v>224</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>19</v>
@@ -14086,22 +14125,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C15" s="4">
         <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E15" s="4">
         <v>7</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>17</v>
@@ -14121,22 +14160,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C16" s="7">
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E16" s="7">
         <v>13</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>17</v>
@@ -14156,22 +14195,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C17" s="4">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E17" s="4">
         <v>36</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>28</v>
@@ -14191,22 +14230,22 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C18" s="7">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E18" s="7">
         <v>3</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>17</v>
@@ -14226,22 +14265,22 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C19" s="4">
         <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E19" s="4">
         <v>21</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>28</v>
@@ -14261,22 +14300,22 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C20" s="7">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E20" s="7">
         <v>27</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>28</v>
@@ -14285,7 +14324,7 @@
         <v>224</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>19</v>
@@ -14296,22 +14335,22 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E21" s="4">
         <v>9</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>17</v>
@@ -14331,22 +14370,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C22" s="7">
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E22" s="7">
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>17</v>
@@ -14366,22 +14405,22 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C23" s="4">
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E23" s="4">
         <v>33</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>28</v>
@@ -14390,7 +14429,7 @@
         <v>269</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>19</v>
@@ -14401,31 +14440,31 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C24" s="7">
         <v>3</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E24" s="7">
         <v>39</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>242</v>
+        <v>737</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>19</v>
@@ -14436,22 +14475,22 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C25" s="4">
         <v>4</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E25" s="4">
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>17</v>
@@ -14460,7 +14499,7 @@
         <v>242</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>19</v>
@@ -14471,22 +14510,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C26" s="7">
         <v>4</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E26" s="7">
         <v>23</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>28</v>
@@ -14495,7 +14534,7 @@
         <v>317</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>19</v>
@@ -14506,31 +14545,31 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E27" s="4">
         <v>29</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>19</v>
@@ -14541,22 +14580,22 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C28" s="7">
         <v>4</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E28" s="7">
         <v>11</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>17</v>
@@ -14576,22 +14615,22 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C29" s="4">
         <v>4</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E29" s="4">
         <v>17</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>17</v>
@@ -14600,7 +14639,7 @@
         <v>239</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>19</v>
@@ -14611,22 +14650,22 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C30" s="7">
         <v>4</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E30" s="7">
         <v>35</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>28</v>
@@ -14635,7 +14674,7 @@
         <v>242</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>19</v>
@@ -14646,22 +14685,22 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C31" s="4">
         <v>5</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E31" s="4">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>17</v>
@@ -14670,7 +14709,7 @@
         <v>224</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>19</v>
@@ -14681,22 +14720,22 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C32" s="7">
         <v>5</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E32" s="7">
         <v>18</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>28</v>
@@ -14705,7 +14744,7 @@
         <v>317</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>19</v>
@@ -14716,31 +14755,31 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C33" s="4">
         <v>5</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E33" s="4">
         <v>24</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>224</v>
+        <v>767</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>19</v>
@@ -14751,31 +14790,31 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C34" s="7">
         <v>5</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E34" s="7">
         <v>30</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>19</v>
@@ -14786,22 +14825,22 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C35" s="4">
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E35" s="4">
         <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>17</v>
@@ -14821,31 +14860,31 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C36" s="7">
         <v>5</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E36" s="7">
         <v>13</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>19</v>
@@ -14856,31 +14895,31 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="E37" s="4">
         <v>37</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>19</v>
@@ -14891,22 +14930,22 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C38" s="7">
         <v>6</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E38" s="7">
         <v>3</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>17</v>
@@ -14915,7 +14954,7 @@
         <v>242</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>19</v>
@@ -14926,22 +14965,22 @@
         <v>35</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C39" s="4">
         <v>6</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E39" s="4">
         <v>15</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>28</v>
@@ -14950,7 +14989,7 @@
         <v>242</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>19</v>
@@ -14961,22 +15000,22 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C40" s="7">
         <v>6</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E40" s="7">
         <v>21</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>28</v>
@@ -14985,7 +15024,7 @@
         <v>224</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>19</v>
@@ -14996,31 +15035,31 @@
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C41" s="4">
         <v>6</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E41" s="4">
         <v>27</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>242</v>
+        <v>792</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>19</v>
@@ -15031,22 +15070,22 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C42" s="7">
         <v>6</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E42" s="7">
         <v>9</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>17</v>
@@ -15055,7 +15094,7 @@
         <v>242</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="K42" s="9" t="s">
         <v>19</v>
@@ -15066,22 +15105,22 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C43" s="4">
         <v>6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E43" s="4">
         <v>33</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>28</v>
@@ -15090,7 +15129,7 @@
         <v>269</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>19</v>
@@ -15101,22 +15140,22 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C44" s="7">
         <v>6</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E44" s="7">
         <v>39</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>28</v>
@@ -15125,7 +15164,7 @@
         <v>224</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="K44" s="9" t="s">
         <v>19</v>
@@ -15136,22 +15175,22 @@
         <v>41</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C45" s="4">
         <v>7</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="E45" s="4">
         <v>17</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>28</v>
@@ -15160,7 +15199,7 @@
         <v>218</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>19</v>
@@ -15171,22 +15210,22 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C46" s="7">
         <v>7</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="E46" s="7">
         <v>5</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>17</v>
@@ -15195,7 +15234,7 @@
         <v>242</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>19</v>
@@ -15206,31 +15245,31 @@
         <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C47" s="4">
         <v>7</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="E47" s="4">
         <v>23</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>19</v>
@@ -15241,22 +15280,22 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C48" s="7">
         <v>7</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="E48" s="7">
         <v>11</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>17</v>
@@ -15276,22 +15315,22 @@
         <v>45</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C49" s="4">
         <v>7</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="E49" s="4">
         <v>29</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>28</v>
@@ -15300,7 +15339,7 @@
         <v>242</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>19</v>
@@ -15311,31 +15350,31 @@
         <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C50" s="7">
         <v>7</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="E50" s="7">
         <v>35</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="K50" s="9" t="s">
         <v>19</v>
@@ -15346,22 +15385,22 @@
         <v>47</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C51" s="4">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E51" s="4">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>17</v>
@@ -15381,22 +15420,22 @@
         <v>48</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C52" s="7">
         <v>8</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E52" s="7">
         <v>7</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>17</v>
@@ -15416,22 +15455,22 @@
         <v>49</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C53" s="4">
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E53" s="4">
         <v>31</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>28</v>
@@ -15451,22 +15490,22 @@
         <v>50</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C54" s="7">
         <v>8</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E54" s="7">
         <v>13</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>17</v>
@@ -15486,31 +15525,31 @@
         <v>51</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C55" s="4">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E55" s="4">
         <v>37</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>224</v>
+        <v>767</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>19</v>
@@ -15521,31 +15560,31 @@
         <v>52</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C56" s="7">
         <v>8</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E56" s="7">
         <v>19</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>827</v>
+        <v>836</v>
       </c>
       <c r="K56" s="9" t="s">
         <v>19</v>
@@ -15556,31 +15595,31 @@
         <v>53</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C57" s="4">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="E57" s="4">
         <v>25</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>828</v>
+        <v>837</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>830</v>
+        <v>839</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>19</v>
@@ -15591,22 +15630,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C58" s="7">
         <v>9</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="E58" s="7">
         <v>3</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>17</v>
@@ -15626,22 +15665,22 @@
         <v>55</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C59" s="4">
         <v>9</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="E59" s="4">
         <v>15</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>28</v>
@@ -15650,7 +15689,7 @@
         <v>269</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>19</v>
@@ -15661,22 +15700,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C60" s="7">
         <v>9</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>305</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>28</v>
@@ -15696,22 +15735,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C61" s="4">
         <v>9</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="E61" s="4">
         <v>26</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>28</v>
@@ -15720,7 +15759,7 @@
         <v>224</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>19</v>
@@ -15731,22 +15770,22 @@
         <v>58</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C62" s="7">
         <v>9</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>305</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>28</v>
@@ -15766,28 +15805,28 @@
         <v>59</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C63" s="4">
         <v>9</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="E63" s="4">
         <v>9</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>19</v>
@@ -15801,31 +15840,31 @@
         <v>60</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C64" s="7">
         <v>9</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="E64" s="7">
         <v>37</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="K64" s="9" t="s">
         <v>19</v>
@@ -15836,22 +15875,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C65" s="4">
         <v>10</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="E65" s="4">
         <v>17</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>28</v>
@@ -15860,7 +15899,7 @@
         <v>224</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>19</v>
@@ -15871,22 +15910,22 @@
         <v>62</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C66" s="7">
         <v>10</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="E66" s="7">
         <v>5</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>17</v>
@@ -15906,22 +15945,22 @@
         <v>63</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C67" s="4">
         <v>10</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="E67" s="4">
         <v>24</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>28</v>
@@ -15930,7 +15969,7 @@
         <v>224</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>19</v>
@@ -15941,22 +15980,22 @@
         <v>64</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C68" s="7">
         <v>10</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="E68" s="7">
         <v>12</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>17</v>
@@ -15965,7 +16004,7 @@
         <v>218</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="K68" s="9" t="s">
         <v>19</v>
@@ -15976,22 +16015,22 @@
         <v>65</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C69" s="4">
         <v>10</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="E69" s="4">
         <v>30</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>28</v>
@@ -16000,7 +16039,7 @@
         <v>224</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>19</v>
@@ -16011,22 +16050,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C70" s="7">
         <v>11</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E70" s="7">
         <v>5</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>17</v>
@@ -16046,22 +16085,22 @@
         <v>67</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C71" s="4">
         <v>11</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E71" s="4">
         <v>11</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>17</v>
@@ -16070,7 +16109,7 @@
         <v>269</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>19</v>
@@ -16081,22 +16120,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C72" s="7">
         <v>11</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E72" s="7">
         <v>23</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>28</v>
@@ -16105,7 +16144,7 @@
         <v>269</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="K72" s="9" t="s">
         <v>19</v>
@@ -16116,22 +16155,22 @@
         <v>69</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C73" s="4">
         <v>11</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E73" s="4">
         <v>17</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>17</v>
@@ -16151,22 +16190,22 @@
         <v>70</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C74" s="7">
         <v>11</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E74" s="7">
         <v>29</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>28</v>
@@ -16175,7 +16214,7 @@
         <v>269</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="K74" s="9" t="s">
         <v>19</v>
@@ -16186,22 +16225,22 @@
         <v>71</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C75" s="4">
         <v>12</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E75" s="4">
         <v>23</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>28</v>
@@ -16210,7 +16249,7 @@
         <v>224</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>19</v>
@@ -16221,31 +16260,31 @@
         <v>72</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C76" s="7">
         <v>12</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E76" s="7">
         <v>5</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="K76" s="9" t="s">
         <v>19</v>
@@ -16256,22 +16295,22 @@
         <v>73</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C77" s="4">
         <v>12</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E77" s="4">
         <v>11</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>17</v>
@@ -16280,7 +16319,7 @@
         <v>224</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>19</v>
@@ -16291,31 +16330,31 @@
         <v>74</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C78" s="7">
         <v>12</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E78" s="7">
         <v>17</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="K78" s="9" t="s">
         <v>19</v>
@@ -16326,22 +16365,22 @@
         <v>75</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E79" s="4">
         <v>29</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>28</v>
@@ -16350,7 +16389,7 @@
         <v>224</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>19</v>
@@ -16361,22 +16400,22 @@
         <v>76</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C80" s="7">
         <v>13</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="E80" s="7">
         <v>17</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>28</v>
@@ -16385,7 +16424,7 @@
         <v>464</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="K80" s="9" t="s">
         <v>19</v>
@@ -16396,22 +16435,22 @@
         <v>77</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C81" s="4">
         <v>13</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="E81" s="4">
         <v>23</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>28</v>
@@ -16420,7 +16459,7 @@
         <v>464</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>19</v>
@@ -16431,22 +16470,22 @@
         <v>78</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C82" s="7">
         <v>13</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="E82" s="7">
         <v>5</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>17</v>
@@ -16455,7 +16494,7 @@
         <v>224</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="K82" s="9" t="s">
         <v>19</v>
@@ -16466,22 +16505,22 @@
         <v>79</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C83" s="4">
         <v>13</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="E83" s="4">
         <v>11</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>17</v>
@@ -16490,7 +16529,7 @@
         <v>242</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>19</v>
@@ -16501,22 +16540,22 @@
         <v>80</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C84" s="7">
         <v>13</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="E84" s="7">
         <v>29</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>28</v>
@@ -16536,22 +16575,22 @@
         <v>81</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C85" s="4">
         <v>14</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="E85" s="4">
         <v>17</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>28</v>
@@ -16560,7 +16599,7 @@
         <v>269</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>19</v>
@@ -16571,31 +16610,31 @@
         <v>82</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="E86" s="7">
         <v>5</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>917</v>
+        <v>926</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="K86" s="9" t="s">
         <v>19</v>
@@ -16606,22 +16645,22 @@
         <v>83</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C87" s="4">
         <v>14</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="E87" s="4">
         <v>11</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>17</v>
@@ -16630,7 +16669,7 @@
         <v>214</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>922</v>
+        <v>931</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>19</v>
@@ -16641,31 +16680,31 @@
         <v>84</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C88" s="7">
         <v>14</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="E88" s="7">
         <v>23</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="K88" s="9" t="s">
         <v>19</v>
@@ -16673,7 +16712,7 @@
     </row>
     <row r="89" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>926</v>
+        <v>935</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
@@ -16681,7 +16720,7 @@
       <c r="E89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="11" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>19</v>
@@ -16727,7 +16766,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>928</v>
+        <v>937</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16742,7 +16781,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -16796,28 +16835,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E5" s="4">
         <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>19</v>
@@ -16831,31 +16870,31 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>936</v>
+        <v>945</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>938</v>
+        <v>947</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>19</v>
@@ -16866,31 +16905,31 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E7" s="4">
         <v>23</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>19</v>
@@ -16901,31 +16940,31 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E8" s="7">
         <v>29</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>19</v>
@@ -16936,22 +16975,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E9" s="4">
         <v>36</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>28</v>
@@ -16960,7 +16999,7 @@
         <v>317</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>19</v>
@@ -16971,31 +17010,31 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E10" s="7">
         <v>11</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>19</v>
@@ -17006,31 +17045,31 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E11" s="4">
         <v>42</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>957</v>
+        <v>966</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>19</v>
@@ -17041,31 +17080,31 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C12" s="7">
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="E12" s="7">
         <v>20</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>959</v>
+        <v>968</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>962</v>
+        <v>971</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>19</v>
@@ -17076,31 +17115,31 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="E13" s="4">
         <v>26</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>963</v>
+        <v>972</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>964</v>
+        <v>973</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>19</v>
@@ -17111,31 +17150,31 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C14" s="7">
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="E14" s="7">
         <v>6</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>19</v>
@@ -17146,31 +17185,31 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C15" s="4">
         <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="E15" s="4">
         <v>33</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>970</v>
+        <v>979</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>971</v>
+        <v>980</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>972</v>
+        <v>981</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>19</v>
@@ -17181,22 +17220,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C16" s="7">
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="E16" s="7">
         <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>28</v>
@@ -17216,31 +17255,31 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C17" s="4">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="E17" s="4">
         <v>12</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>977</v>
+        <v>986</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>972</v>
+        <v>981</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>978</v>
+        <v>987</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>19</v>
@@ -17251,31 +17290,31 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C18" s="7">
         <v>2</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="E18" s="7">
         <v>40</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>979</v>
+        <v>988</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>980</v>
+        <v>989</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>981</v>
+        <v>990</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>19</v>
@@ -17286,22 +17325,22 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C19" s="4">
         <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>17</v>
@@ -17321,31 +17360,31 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C20" s="7">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E20" s="7">
         <v>27</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>985</v>
+        <v>994</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>19</v>
@@ -17356,31 +17395,31 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E21" s="4">
         <v>8</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>988</v>
+        <v>997</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>989</v>
+        <v>998</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>991</v>
+        <v>1000</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>19</v>
@@ -17391,28 +17430,28 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C22" s="7">
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E22" s="7">
         <v>33</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>19</v>
@@ -17426,31 +17465,31 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C23" s="4">
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E23" s="4">
         <v>14</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>995</v>
+        <v>1004</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>997</v>
+        <v>1006</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>998</v>
+        <v>1007</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>19</v>
@@ -17461,31 +17500,31 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C24" s="7">
         <v>3</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E24" s="7">
         <v>39</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>999</v>
+        <v>1008</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>1000</v>
+        <v>1009</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>1001</v>
+        <v>1010</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>19</v>
@@ -17496,31 +17535,31 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E25" s="4">
         <v>21</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>1004</v>
+        <v>1013</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1005</v>
+        <v>1014</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>1006</v>
+        <v>1015</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>19</v>
@@ -17531,22 +17570,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C26" s="7">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>305</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>1008</v>
+        <v>1017</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>28</v>
@@ -17566,31 +17605,31 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E27" s="4">
         <v>4</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1011</v>
+        <v>1020</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>19</v>
@@ -17601,31 +17640,31 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C28" s="7">
         <v>4</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E28" s="7">
         <v>23</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1014</v>
+        <v>1023</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>1015</v>
+        <v>1024</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>1016</v>
+        <v>1025</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>1017</v>
+        <v>1026</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>19</v>
@@ -17636,31 +17675,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C29" s="4">
         <v>4</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E29" s="4">
         <v>30</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>1019</v>
+        <v>1028</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>1016</v>
+        <v>1025</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>1020</v>
+        <v>1029</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>19</v>
@@ -17671,31 +17710,31 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C30" s="7">
         <v>4</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E30" s="7">
         <v>10</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1021</v>
+        <v>1030</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>1022</v>
+        <v>1031</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>19</v>
@@ -17706,31 +17745,31 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E31" s="4">
         <v>36</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1023</v>
+        <v>1032</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>1025</v>
+        <v>1034</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>1026</v>
+        <v>1035</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>19</v>
@@ -17741,31 +17780,31 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C32" s="7">
         <v>4</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E32" s="7">
         <v>16</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>1028</v>
+        <v>1037</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>19</v>
@@ -17776,31 +17815,31 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C33" s="4">
         <v>4</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E33" s="4">
         <v>42</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>1031</v>
+        <v>1040</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>19</v>
@@ -17811,31 +17850,31 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C34" s="7">
         <v>4</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="E34" s="7">
         <v>44</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>1035</v>
+        <v>1045</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>1036</v>
+        <v>1046</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>19</v>
@@ -17846,31 +17885,31 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C35" s="4">
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="E35" s="4">
         <v>23</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>19</v>
@@ -17881,31 +17920,31 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C36" s="7">
         <v>5</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="E36" s="7">
         <v>29</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1041</v>
+        <v>1051</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>1042</v>
+        <v>1052</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>1044</v>
+        <v>1054</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>19</v>
@@ -17916,28 +17955,28 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="E37" s="4">
         <v>35</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1045</v>
+        <v>1055</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>19</v>
@@ -17951,22 +17990,22 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C38" s="7">
         <v>5</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="E38" s="7">
         <v>8</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>1048</v>
+        <v>1058</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>17</v>
@@ -17986,31 +18025,31 @@
         <v>35</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C39" s="4">
         <v>5</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="E39" s="4">
         <v>14</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1049</v>
+        <v>1059</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>1051</v>
+        <v>1061</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>19</v>
@@ -18021,31 +18060,31 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C40" s="7">
         <v>5</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="E40" s="7">
         <v>16</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>1052</v>
+        <v>1062</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>1053</v>
+        <v>1063</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>1054</v>
+        <v>1064</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>19</v>
@@ -18056,31 +18095,31 @@
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C41" s="4">
         <v>5</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="E41" s="4">
         <v>41</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>1057</v>
+        <v>1067</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>19</v>
@@ -18091,31 +18130,31 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C42" s="7">
         <v>6</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E42" s="7">
         <v>14</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1059</v>
+        <v>1069</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>1061</v>
+        <v>1071</v>
       </c>
       <c r="K42" s="9" t="s">
         <v>19</v>
@@ -18126,31 +18165,31 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C43" s="4">
         <v>6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E43" s="4">
         <v>2</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>1062</v>
+        <v>1072</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>19</v>
@@ -18161,31 +18200,31 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C44" s="7">
         <v>6</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E44" s="7">
         <v>20</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="K44" s="9" t="s">
         <v>19</v>
@@ -18196,22 +18235,22 @@
         <v>41</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C45" s="4">
         <v>6</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E45" s="4">
         <v>25</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>28</v>
@@ -18220,7 +18259,7 @@
         <v>464</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>19</v>
@@ -18231,31 +18270,31 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C46" s="7">
         <v>6</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E46" s="7">
         <v>7</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>1072</v>
+        <v>1082</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>1074</v>
+        <v>1084</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>19</v>
@@ -18266,31 +18305,31 @@
         <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C47" s="4">
         <v>6</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E47" s="4">
         <v>31</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>1076</v>
+        <v>1086</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>1077</v>
+        <v>1087</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>19</v>
@@ -18301,31 +18340,31 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C48" s="7">
         <v>6</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E48" s="7">
         <v>37</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>1078</v>
+        <v>1088</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>1079</v>
+        <v>1089</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>19</v>
@@ -18336,28 +18375,28 @@
         <v>45</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C49" s="4">
         <v>7</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="E49" s="4">
         <v>4</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>1082</v>
+        <v>1092</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>1083</v>
+        <v>1093</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>19</v>
@@ -18371,31 +18410,31 @@
         <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C50" s="7">
         <v>7</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="E50" s="7">
         <v>16</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>1085</v>
+        <v>1095</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="K50" s="9" t="s">
         <v>19</v>
@@ -18406,28 +18445,28 @@
         <v>47</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C51" s="4">
         <v>7</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="E51" s="4">
         <v>5</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>19</v>
@@ -18441,31 +18480,31 @@
         <v>48</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C52" s="7">
         <v>7</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="E52" s="7">
         <v>22</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1089</v>
+        <v>1099</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="K52" s="9" t="s">
         <v>19</v>
@@ -18476,22 +18515,22 @@
         <v>49</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C53" s="4">
         <v>7</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="E53" s="4">
         <v>27</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>28</v>
@@ -18511,31 +18550,31 @@
         <v>50</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C54" s="7">
         <v>7</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="E54" s="7">
         <v>33</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>19</v>
@@ -18546,22 +18585,22 @@
         <v>51</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C55" s="4">
         <v>7</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="E55" s="4">
         <v>39</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>1097</v>
+        <v>1107</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>28</v>
@@ -18581,31 +18620,31 @@
         <v>52</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C56" s="7">
         <v>8</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="E56" s="7">
         <v>17</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>1101</v>
+        <v>1111</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
       <c r="K56" s="9" t="s">
         <v>19</v>
@@ -18616,22 +18655,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C57" s="4">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="E57" s="4">
         <v>23</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>28</v>
@@ -18651,31 +18690,31 @@
         <v>54</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C58" s="7">
         <v>8</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="E58" s="7">
         <v>6</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>1107</v>
+        <v>1117</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="K58" s="9" t="s">
         <v>19</v>
@@ -18686,31 +18725,31 @@
         <v>55</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C59" s="4">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="E59" s="4">
         <v>29</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>19</v>
@@ -18721,31 +18760,31 @@
         <v>56</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C60" s="7">
         <v>8</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="E60" s="7">
         <v>11</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
       <c r="K60" s="9" t="s">
         <v>19</v>
@@ -18756,31 +18795,31 @@
         <v>57</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C61" s="4">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
       <c r="E61" s="4">
         <v>35</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>1117</v>
+        <v>1127</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>19</v>
@@ -18791,31 +18830,31 @@
         <v>58</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C62" s="7">
         <v>9</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
       <c r="E62" s="7">
         <v>13</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="K62" s="9" t="s">
         <v>19</v>
@@ -18826,28 +18865,28 @@
         <v>59</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C63" s="4">
         <v>9</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
       <c r="E63" s="4">
         <v>6</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>1122</v>
+        <v>1132</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>1123</v>
+        <v>1133</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>1124</v>
+        <v>1134</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>19</v>
@@ -18861,31 +18900,31 @@
         <v>60</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C64" s="7">
         <v>9</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
       <c r="E64" s="7">
         <v>19</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>1124</v>
+        <v>1134</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
       <c r="K64" s="9" t="s">
         <v>19</v>
@@ -18896,31 +18935,31 @@
         <v>61</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C65" s="4">
         <v>9</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
       <c r="E65" s="4">
         <v>25</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>1128</v>
+        <v>1138</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>19</v>
@@ -18931,31 +18970,31 @@
         <v>62</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C66" s="7">
         <v>10</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="E66" s="7">
         <v>2</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>1134</v>
+        <v>1144</v>
       </c>
       <c r="K66" s="9" t="s">
         <v>19</v>
@@ -18966,31 +19005,31 @@
         <v>63</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C67" s="4">
         <v>10</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="E67" s="4">
         <v>19</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>1138</v>
+        <v>1148</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>19</v>
@@ -19001,31 +19040,31 @@
         <v>64</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C68" s="7">
         <v>10</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="E68" s="7">
         <v>7</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>1141</v>
+        <v>1151</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="K68" s="9" t="s">
         <v>19</v>
@@ -19036,31 +19075,31 @@
         <v>65</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C69" s="4">
         <v>10</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="E69" s="4">
         <v>25</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>1144</v>
+        <v>1154</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>19</v>
@@ -19071,31 +19110,31 @@
         <v>66</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C70" s="7">
         <v>10</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="E70" s="7">
         <v>13</v>
       </c>
       <c r="F70" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" s="9" t="s">
         <v>1147</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>1148</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I70" s="9" t="s">
-        <v>1137</v>
-      </c>
       <c r="J70" s="7" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="K70" s="9" t="s">
         <v>19</v>
@@ -19106,31 +19145,31 @@
         <v>67</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C71" s="4">
         <v>11</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="E71" s="4">
         <v>2</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>1151</v>
+        <v>1161</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>19</v>
@@ -19141,31 +19180,31 @@
         <v>68</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C72" s="7">
         <v>11</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="E72" s="7">
         <v>8</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="K72" s="9" t="s">
         <v>19</v>
@@ -19176,31 +19215,31 @@
         <v>69</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C73" s="4">
         <v>11</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="E73" s="4">
         <v>21</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>19</v>
@@ -19211,31 +19250,31 @@
         <v>70</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C74" s="7">
         <v>11</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="E74" s="7">
         <v>27</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>1162</v>
+        <v>1172</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>1163</v>
+        <v>1173</v>
       </c>
       <c r="K74" s="9" t="s">
         <v>19</v>
@@ -19246,31 +19285,31 @@
         <v>71</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C75" s="4">
         <v>11</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="E75" s="4">
         <v>14</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>1164</v>
+        <v>1174</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>1166</v>
+        <v>1176</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>19</v>
@@ -19281,31 +19320,31 @@
         <v>72</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C76" s="7">
         <v>12</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="E76" s="7">
         <v>14</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>1171</v>
+        <v>1181</v>
       </c>
       <c r="K76" s="9" t="s">
         <v>19</v>
@@ -19316,31 +19355,31 @@
         <v>73</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C77" s="4">
         <v>12</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="E77" s="4">
         <v>2</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>1172</v>
+        <v>1182</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>1001</v>
+        <v>1184</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>19</v>
+        <v>1185</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>19</v>
@@ -19351,31 +19390,31 @@
         <v>74</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C78" s="7">
         <v>12</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="E78" s="7">
         <v>20</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>1175</v>
+        <v>1187</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>1176</v>
+        <v>1188</v>
       </c>
       <c r="K78" s="9" t="s">
         <v>19</v>
@@ -19386,31 +19425,31 @@
         <v>75</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="E79" s="4">
         <v>8</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>952</v>
+        <v>1191</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>19</v>
@@ -19421,31 +19460,31 @@
         <v>76</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C80" s="7">
         <v>12</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="E80" s="7">
         <v>26</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="K80" s="9" t="s">
         <v>19</v>
@@ -19456,31 +19495,31 @@
         <v>77</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C81" s="4">
         <v>13</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="E81" s="4">
         <v>13</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>19</v>
@@ -19491,28 +19530,28 @@
         <v>78</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C82" s="7">
         <v>13</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="E82" s="7">
         <v>2</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="J82" s="7" t="s">
         <v>19</v>
@@ -19526,31 +19565,31 @@
         <v>79</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C83" s="4">
         <v>13</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="E83" s="4">
         <v>7</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>17</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>19</v>
@@ -19561,22 +19600,22 @@
         <v>80</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C84" s="7">
         <v>13</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="E84" s="7">
         <v>18</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>28</v>
@@ -19593,7 +19632,7 @@
     </row>
     <row r="85" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
@@ -19601,7 +19640,7 @@
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="11" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="H85" s="12" t="s">
         <v>19</v>
@@ -19647,7 +19686,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19662,7 +19701,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -19716,22 +19755,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E5" s="4">
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>17</v>
@@ -19751,22 +19790,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E6" s="7">
         <v>24</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>28</v>
@@ -19786,22 +19825,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E7" s="4">
         <v>28</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>28</v>
@@ -19821,22 +19860,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E8" s="7">
         <v>8</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>17</v>
@@ -19856,22 +19895,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E9" s="4">
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>17</v>
@@ -19891,22 +19930,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E10" s="7">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>17</v>
@@ -19926,22 +19965,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="E11" s="4">
         <v>42</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>28</v>
@@ -19961,22 +20000,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C12" s="7">
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E12" s="7">
         <v>23</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>28</v>
@@ -19996,22 +20035,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E13" s="4">
         <v>3</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>17</v>
@@ -20031,22 +20070,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C14" s="7">
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E14" s="7">
         <v>29</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>28</v>
@@ -20066,22 +20105,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C15" s="4">
         <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E15" s="4">
         <v>10</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>17</v>
@@ -20101,22 +20140,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C16" s="7">
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E16" s="7">
         <v>35</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>28</v>
@@ -20136,22 +20175,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C17" s="4">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E17" s="4">
         <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>17</v>
@@ -20171,22 +20210,22 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C18" s="7">
         <v>2</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E18" s="7">
         <v>41</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>28</v>
@@ -20206,22 +20245,22 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C19" s="4">
         <v>2</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="E19" s="4">
         <v>17</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>17</v>
@@ -20241,22 +20280,22 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C20" s="7">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E20" s="7">
         <v>5</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1232</v>
+        <v>1245</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>17</v>
@@ -20265,7 +20304,7 @@
         <v>221</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>19</v>
@@ -20276,22 +20315,22 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E21" s="4">
         <v>11</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>17</v>
@@ -20311,22 +20350,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C22" s="7">
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E22" s="7">
         <v>24</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>28</v>
@@ -20346,22 +20385,22 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C23" s="4">
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E23" s="4">
         <v>30</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>28</v>
@@ -20381,22 +20420,22 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C24" s="7">
         <v>3</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E24" s="7">
         <v>17</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1241</v>
+        <v>1254</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>1242</v>
+        <v>1255</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>17</v>
@@ -20416,22 +20455,22 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E25" s="4">
         <v>34</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1243</v>
+        <v>1256</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>28</v>
@@ -20451,22 +20490,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C26" s="7">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="E26" s="7">
         <v>38</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>28</v>
@@ -20486,22 +20525,22 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1249</v>
+        <v>1262</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>17</v>
@@ -20521,22 +20560,22 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C28" s="7">
         <v>4</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="E28" s="7">
         <v>20</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>28</v>
@@ -20556,22 +20595,22 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C29" s="4">
         <v>4</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="E29" s="4">
         <v>26</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>1253</v>
+        <v>1266</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>28</v>
@@ -20591,22 +20630,22 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C30" s="7">
         <v>4</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="E30" s="7">
         <v>8</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>17</v>
@@ -20626,22 +20665,22 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="E31" s="4">
         <v>32</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1256</v>
+        <v>1269</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>28</v>
@@ -20661,22 +20700,22 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C32" s="7">
         <v>4</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="E32" s="7">
         <v>14</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>17</v>
@@ -20696,22 +20735,22 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C33" s="4">
         <v>4</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="E33" s="4">
         <v>37</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>28</v>
@@ -20731,22 +20770,22 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C34" s="7">
         <v>5</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E34" s="7">
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>28</v>
@@ -20766,22 +20805,22 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C35" s="4">
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E35" s="4">
         <v>3</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>17</v>
@@ -20801,22 +20840,22 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C36" s="7">
         <v>5</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E36" s="7">
         <v>26</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>28</v>
@@ -20836,22 +20875,22 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E37" s="4">
         <v>9</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1269</v>
+        <v>1282</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>1270</v>
+        <v>1283</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>17</v>
@@ -20871,22 +20910,22 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C38" s="7">
         <v>5</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E38" s="7">
         <v>32</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>1271</v>
+        <v>1284</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>28</v>
@@ -20906,22 +20945,22 @@
         <v>35</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C39" s="4">
         <v>5</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E39" s="4">
         <v>15</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1273</v>
+        <v>1286</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>17</v>
@@ -20941,22 +20980,22 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C40" s="7">
         <v>5</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E40" s="7">
         <v>38</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>1276</v>
+        <v>1289</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>28</v>
@@ -20976,22 +21015,22 @@
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C41" s="4">
         <v>5</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="E41" s="4">
         <v>41</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>28</v>
@@ -21011,22 +21050,22 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C42" s="7">
         <v>6</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E42" s="7">
         <v>10</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>28</v>
@@ -21046,22 +21085,22 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C43" s="4">
         <v>6</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E43" s="4">
         <v>16</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>28</v>
@@ -21081,22 +21120,22 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C44" s="7">
         <v>6</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E44" s="7">
         <v>21</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>1285</v>
+        <v>1298</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>28</v>
@@ -21116,22 +21155,22 @@
         <v>41</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C45" s="4">
         <v>6</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E45" s="4">
         <v>27</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>1286</v>
+        <v>1299</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>28</v>
@@ -21151,22 +21190,22 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C46" s="7">
         <v>6</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E46" s="7">
         <v>4</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>1288</v>
+        <v>1301</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>17</v>
@@ -21186,22 +21225,22 @@
         <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C47" s="4">
         <v>6</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E47" s="4">
         <v>34</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>1291</v>
+        <v>1304</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>28</v>
@@ -21221,22 +21260,22 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C48" s="7">
         <v>7</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="E48" s="7">
         <v>1</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>1293</v>
+        <v>1306</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>1294</v>
+        <v>1307</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>17</v>
@@ -21256,22 +21295,22 @@
         <v>45</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C49" s="4">
         <v>7</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="E49" s="4">
         <v>18</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>1296</v>
+        <v>1309</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>28</v>
@@ -21291,22 +21330,22 @@
         <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C50" s="7">
         <v>7</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="E50" s="7">
         <v>22</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>1297</v>
+        <v>1310</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>1298</v>
+        <v>1311</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>28</v>
@@ -21326,22 +21365,22 @@
         <v>47</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C51" s="4">
         <v>7</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="E51" s="4">
         <v>6</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1299</v>
+        <v>1312</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>1300</v>
+        <v>1313</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>17</v>
@@ -21361,22 +21400,22 @@
         <v>48</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C52" s="7">
         <v>7</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="E52" s="7">
         <v>27</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1301</v>
+        <v>1314</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>1302</v>
+        <v>1315</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>28</v>
@@ -21396,22 +21435,22 @@
         <v>49</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C53" s="4">
         <v>7</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="E53" s="4">
         <v>12</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>1303</v>
+        <v>1316</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>1304</v>
+        <v>1317</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>17</v>
@@ -21431,22 +21470,22 @@
         <v>50</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C54" s="7">
         <v>7</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="E54" s="7">
         <v>33</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1305</v>
+        <v>1318</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>28</v>
@@ -21466,22 +21505,22 @@
         <v>51</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C55" s="4">
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="E55" s="4">
         <v>3</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>1308</v>
+        <v>1321</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>17</v>
@@ -21501,22 +21540,22 @@
         <v>52</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C56" s="7">
         <v>8</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="E56" s="7">
         <v>26</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>1311</v>
+        <v>1324</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>28</v>
@@ -21536,22 +21575,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C57" s="4">
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="E57" s="4">
         <v>7</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>1312</v>
+        <v>1325</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>1313</v>
+        <v>1326</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>17</v>
@@ -21571,22 +21610,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C58" s="7">
         <v>8</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="E58" s="7">
         <v>13</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1314</v>
+        <v>1327</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>1315</v>
+        <v>1328</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>17</v>
@@ -21606,22 +21645,22 @@
         <v>55</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C59" s="4">
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="E59" s="4">
         <v>31</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>1316</v>
+        <v>1329</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>1317</v>
+        <v>1330</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>28</v>
@@ -21641,22 +21680,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C60" s="7">
         <v>8</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="E60" s="7">
         <v>19</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1318</v>
+        <v>1331</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>1319</v>
+        <v>1332</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>17</v>
@@ -21676,22 +21715,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C61" s="4">
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="E61" s="4">
         <v>37</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>1320</v>
+        <v>1333</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>28</v>
@@ -21711,22 +21750,22 @@
         <v>58</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C62" s="7">
         <v>9</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="E62" s="7">
         <v>6</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>1324</v>
+        <v>1337</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>17</v>
@@ -21746,22 +21785,22 @@
         <v>59</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C63" s="4">
         <v>9</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="E63" s="4">
         <v>11</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>28</v>
@@ -21781,22 +21820,22 @@
         <v>60</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C64" s="7">
         <v>9</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="E64" s="7">
         <v>17</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>1327</v>
+        <v>1340</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>1328</v>
+        <v>1341</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>28</v>
@@ -21816,22 +21855,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C65" s="4">
         <v>9</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="E65" s="4">
         <v>22</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>1329</v>
+        <v>1342</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>1330</v>
+        <v>1343</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>28</v>
@@ -21851,22 +21890,22 @@
         <v>62</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C66" s="7">
         <v>9</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="E66" s="7">
         <v>28</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>1331</v>
+        <v>1344</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>1332</v>
+        <v>1345</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>28</v>
@@ -21886,22 +21925,22 @@
         <v>63</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C67" s="4">
         <v>10</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="E67" s="4">
         <v>15</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>1335</v>
+        <v>1348</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>28</v>
@@ -21921,22 +21960,22 @@
         <v>64</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C68" s="7">
         <v>10</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="E68" s="7">
         <v>22</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>1336</v>
+        <v>1349</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>1337</v>
+        <v>1350</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>28</v>
@@ -21956,22 +21995,22 @@
         <v>65</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C69" s="4">
         <v>10</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="E69" s="4">
         <v>4</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>1338</v>
+        <v>1351</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>1339</v>
+        <v>1352</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>17</v>
@@ -21991,22 +22030,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C70" s="7">
         <v>10</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="E70" s="7">
         <v>10</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>1340</v>
+        <v>1353</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>1341</v>
+        <v>1354</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>17</v>
@@ -22026,22 +22065,22 @@
         <v>67</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C71" s="4">
         <v>10</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="E71" s="4">
         <v>28</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>1342</v>
+        <v>1355</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>1343</v>
+        <v>1356</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>28</v>
@@ -22061,22 +22100,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C72" s="7">
         <v>11</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="E72" s="7">
         <v>17</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>1345</v>
+        <v>1358</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>28</v>
@@ -22085,7 +22124,7 @@
         <v>224</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>1347</v>
+        <v>1360</v>
       </c>
       <c r="K72" s="9" t="s">
         <v>19</v>
@@ -22096,22 +22135,22 @@
         <v>69</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C73" s="4">
         <v>11</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="E73" s="4">
         <v>6</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>1348</v>
+        <v>1361</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>17</v>
@@ -22131,22 +22170,22 @@
         <v>70</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C74" s="7">
         <v>11</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="E74" s="7">
         <v>23</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>1350</v>
+        <v>1363</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>28</v>
@@ -22166,22 +22205,22 @@
         <v>71</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C75" s="4">
         <v>11</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="E75" s="4">
         <v>12</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>1352</v>
+        <v>1365</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>1353</v>
+        <v>1366</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>17</v>
@@ -22201,22 +22240,22 @@
         <v>72</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C76" s="7">
         <v>11</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="E76" s="7">
         <v>29</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>1355</v>
+        <v>1368</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>28</v>
@@ -22236,22 +22275,22 @@
         <v>73</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C77" s="4">
         <v>12</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="E77" s="4">
         <v>18</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>1357</v>
+        <v>1370</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>28</v>
@@ -22271,22 +22310,22 @@
         <v>74</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C78" s="7">
         <v>12</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="E78" s="7">
         <v>6</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>1359</v>
+        <v>1372</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>1360</v>
+        <v>1373</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>17</v>
@@ -22306,22 +22345,22 @@
         <v>75</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="E79" s="4">
         <v>12</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>1362</v>
+        <v>1375</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>17</v>
@@ -22341,22 +22380,22 @@
         <v>76</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C80" s="7">
         <v>12</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="E80" s="7">
         <v>24</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>1363</v>
+        <v>1376</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>1364</v>
+        <v>1377</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>28</v>
@@ -22376,22 +22415,22 @@
         <v>77</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C81" s="4">
         <v>12</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="E81" s="4">
         <v>28</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>1366</v>
+        <v>1379</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>28</v>
@@ -22411,22 +22450,22 @@
         <v>78</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C82" s="7">
         <v>13</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="E82" s="7">
         <v>9</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>1368</v>
+        <v>1381</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>1369</v>
+        <v>1382</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>28</v>
@@ -22446,22 +22485,22 @@
         <v>79</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C83" s="4">
         <v>13</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="E83" s="4">
         <v>14</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>28</v>
@@ -22481,22 +22520,22 @@
         <v>80</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C84" s="7">
         <v>13</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="E84" s="7">
         <v>3</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>17</v>
@@ -22516,22 +22555,22 @@
         <v>81</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="C85" s="4">
         <v>13</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="E85" s="4">
         <v>20</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>28</v>
@@ -22548,7 +22587,7 @@
     </row>
     <row r="86" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
@@ -22556,7 +22595,7 @@
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="11" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
       <c r="H86" s="12" t="s">
         <v>19</v>
